--- a/jogos_2025-06-01.xlsx
+++ b/jogos_2025-06-01.xlsx
@@ -643,16 +643,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Mt Druitt Town</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="N2" t="n">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.76</v>
+        <v>3.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.46</v>
+        <v>10.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -696,56 +696,56 @@
         <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['39', '42', '72']</t>
+          <t>['18', '35']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45809.08333333334</v>
@@ -772,19 +772,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3.66</v>
+        <v>5.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>8.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.35</v>
+        <v>6.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['39', '42', '72']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['43', '45+2', '90+6']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['38', '86']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45809.08333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mt Druitt Town</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8</v>
+        <v>3.66</v>
       </c>
       <c r="N4" t="n">
-        <v>9.5</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="P4" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.5</v>
+        <v>3.35</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.94</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['18', '35']</t>
+          <t>['43', '45+2', '90+6']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['38', '86']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45809.08333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>2.83</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA10" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['31', '89']</t>
+          <t>['26', '32', '61']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '89']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45809.1875</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.33</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X11" t="n">
-        <v>4.6</v>
+        <v>2.83</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>2.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.6</v>
+        <v>3.96</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['26', '32', '61']</t>
+          <t>['31', '89']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['19', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45809.1875</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>3.03</v>
       </c>
       <c r="M12" t="n">
-        <v>3.77</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.1</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.3</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X12" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
         <v>1.95</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45809.29166666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.69</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>1.34</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['52', '60', '69', '88']</t>
+          <t>['20', '69', '90+5']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['23', '44', '57']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>3.84</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.71</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45809.29166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,16 +2320,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -2346,52 +2346,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.03</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="AB15" t="n">
         <v>1.3</v>
@@ -2400,29 +2400,29 @@
         <v>1.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['52', '60', '69', '88']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.8</v>
+        <v>2.71</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45809.29166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.34</v>
+        <v>4.75</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['20', '69', '90+5']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['23', '44', '57']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.84</v>
+        <v>1.51</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45809.29166666666</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,65 +2991,65 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>3.52</v>
       </c>
       <c r="M20" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O20" t="n">
         <v>4.2</v>
       </c>
-      <c r="N20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.95</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['9', '33', '85']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.48</v>
+        <v>2.55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45809.375</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,55 +3120,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>5.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
         <v>1.6</v>
@@ -3178,25 +3178,25 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['9', '33', '85']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['24', '42', '90+8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.48</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45809.375</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.52</v>
+        <v>2.27</v>
       </c>
       <c r="M23" t="n">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>1.89</v>
+        <v>2.57</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '42', '90+8']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45809.375</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>2.01</v>
       </c>
       <c r="O26" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>2.59</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>3.31</v>
       </c>
       <c r="T26" t="n">
-        <v>2.87</v>
+        <v>2.57</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
         <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['87', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.32</v>
+        <v>1.29</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45809.41666666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['31', '52', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45809.41666666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45809.41666666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="M29" t="n">
         <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.3</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.6</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4215,20 +4215,20 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['87', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45809.41666666666</v>
@@ -4281,58 +4281,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
         <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="O30" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.88</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.3</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD30" t="n">
         <v>1.95</v>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45809.41666666666</v>
@@ -4890,33 +4890,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>2.87</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.92</v>
+        <v>2.23</v>
       </c>
       <c r="O35" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X35" t="n">
         <v>3.1</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.25</v>
       </c>
-      <c r="X35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['7', '34', '65']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI35" t="n">
         <v>2.15</v>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['45+4', '57']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45809.47916666666</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5055,43 +5055,43 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>2.92</v>
       </c>
       <c r="O36" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="R36" t="n">
         <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T36" t="n">
         <v>2.45</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
         <v>1.76</v>
@@ -5100,20 +5100,20 @@
         <v>1.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['74', '90+1']</t>
+          <t>['45+4', '57']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45809.47916666666</v>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,55 +5184,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.87</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="N37" t="n">
-        <v>2.23</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="R37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.25</v>
       </c>
       <c r="AC37" t="n">
         <v>1.8</v>
@@ -5242,25 +5242,25 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['7', '34', '65']</t>
+          <t>['74', '90+1']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45809.47916666666</v>
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH38" t="n">
         <v>3</v>
       </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['24', '45+1', '72']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['68', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI38" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45809.5</v>
@@ -5406,119 +5406,119 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>8</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="Y39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.1</v>
       </c>
-      <c r="U39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.86</v>
-      </c>
       <c r="AA39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['4', '14', '22', '41']</t>
+          <t>['31', '81', '90+5']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['30', '40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45809.5</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>9.699999999999999</v>
+        <v>2.51</v>
       </c>
       <c r="M40" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N40" t="n">
-        <v>1.22</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.62</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['24', '45+1', '72']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['68', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI40" t="n">
         <v>2</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X40" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['7', '50', '67', '86']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AJ40" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45809.5</v>
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N41" t="n">
-        <v>7.3</v>
+        <v>1.22</v>
       </c>
       <c r="O41" t="n">
-        <v>1.83</v>
+        <v>9</v>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>1.62</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X41" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['7', '50', '67', '86']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.07</v>
+        <v>3.8</v>
       </c>
       <c r="AH41" t="n">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45809.5</v>
@@ -5793,35 +5793,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="M42" t="n">
-        <v>3.66</v>
+        <v>5.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.59</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S42" t="n">
         <v>3.8</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="Z42" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA42" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['31', '81', '90+5']</t>
+          <t>['4', '14', '22', '41']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '40']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45809.5</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,16 +5932,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O43" t="n">
         <v>3.4</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O43" t="n">
-        <v>4.21</v>
-      </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="R43" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T43" t="n">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="U43" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X43" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['33', '73']</t>
+          <t>['61', '69']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,87 +6061,87 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6150,20 +6150,20 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '73']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45809.5</v>
@@ -6309,29 +6309,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S46" t="n">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="U46" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W46" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="X46" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.87</v>
+        <v>4.45</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.13</v>
+        <v>1.68</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45809.52083333334</v>
@@ -6438,30 +6438,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="O47" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="P47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z47" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q47" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA47" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45809.52083333334</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
         <v>1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="O50" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P50" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R50" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T50" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="U50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>['11', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.42</v>
       </c>
-      <c r="V50" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y50" t="n">
+      <c r="AI50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>1.85</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>['8', '26', '71']</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45809.5625</v>
@@ -6964,109 +6964,109 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N51" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['26', '40']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['16', '60', '81']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['23', '45']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AI51" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45809.5625</v>
@@ -7083,35 +7083,35 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA52" t="n">
         <v>3</v>
       </c>
-      <c r="M52" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB52" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['8', '26', '71']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45809.5625</v>
@@ -7212,29 +7212,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.19</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>6.7</v>
+        <v>3.24</v>
       </c>
       <c r="N53" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="O53" t="n">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="R53" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S53" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="T53" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="U53" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="V53" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W53" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="X53" t="n">
-        <v>5.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AA53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['8', '57']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>4.5</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45809.5625</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G54" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="M54" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N54" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="O54" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="P54" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.25</v>
       </c>
-      <c r="S54" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X54" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC54" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['16', '60', '81']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '45']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45809.5625</v>
@@ -7480,69 +7480,69 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
         <v>3</v>
       </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2</v>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="M55" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="N55" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="O55" t="n">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="P55" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="R55" t="n">
         <v>1.25</v>
       </c>
       <c r="S55" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U55" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V55" t="n">
         <v>1.03</v>
       </c>
       <c r="W55" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X55" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Y55" t="n">
         <v>1.8</v>
@@ -7551,38 +7551,38 @@
         <v>1.94</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['38', '45+3', '70']</t>
+          <t>['4', '25', '32', '89']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AI55" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45809.5625</v>
@@ -7599,97 +7599,97 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>3</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>5.5</v>
-      </c>
       <c r="M56" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="O56" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="P56" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="R56" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S56" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="T56" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="U56" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="V56" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W56" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="X56" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7698,20 +7698,20 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['4', '25', '32', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>2.65</v>
+        <v>1.36</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AI56" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45809.5625</v>
@@ -7728,32 +7728,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
+        <v>1.19</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="N57" t="n">
+        <v>12</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X57" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA57" t="n">
         <v>2.25</v>
       </c>
-      <c r="O57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AB57" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
+          <t>['8', '57']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG57" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.33</v>
+        <v>4.33</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45809.5625</v>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="M58" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N58" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="O58" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="P58" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="S58" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="T58" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="U58" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="V58" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="X58" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AA58" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['26', '40']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG58" t="n">
         <v>1.13</v>
       </c>
       <c r="AH58" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45809.5625</v>
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="N59" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="O59" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="P59" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T59" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q59" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X59" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD59" t="n">
         <v>1.55</v>
       </c>
-      <c r="V59" t="n">
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>['38', '45+3', '70']</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH59" t="n">
         <v>1.04</v>
       </c>
-      <c r="W59" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>['11', '90+6']</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AI59" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45809.5625</v>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -8534,87 +8534,87 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
+          <t>['50', '65', '78']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45809.60416666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,106 +8770,106 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X65" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="n">
-        <v>3</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X65" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>3</v>
-      </c>
       <c r="AB65" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['20', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['11', '46', '49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG65" t="n">
         <v>1.25</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AJ65" t="n">
         <v>2.5</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,25 +8899,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8925,80 +8925,80 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="M66" t="n">
-        <v>3.93</v>
+        <v>3.55</v>
       </c>
       <c r="N66" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="O66" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="P66" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="R66" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S66" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="T66" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U66" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="V66" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W66" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X66" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB66" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC66" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC66" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD66" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '80']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '46', '49']</t>
         </is>
       </c>
       <c r="AG66" t="n">
         <v>1.25</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ66" t="n">
         <v>2.5</v>
@@ -9286,25 +9286,25 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.39</v>
+        <v>2.89</v>
       </c>
       <c r="N69" t="n">
-        <v>5.1</v>
+        <v>3.14</v>
       </c>
       <c r="O69" t="n">
-        <v>2.72</v>
+        <v>3.06</v>
       </c>
       <c r="P69" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="R69" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="S69" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="T69" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U69" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V69" t="n">
         <v>1.14</v>
       </c>
       <c r="W69" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X69" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AA69" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AB69" t="n">
         <v>1.13</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9375,20 +9375,20 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['22', '26']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH69" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI69" t="n">
         <v>1.83</v>
       </c>
-      <c r="AI69" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ69" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45809.64583333334</v>
@@ -9544,19 +9544,19 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="M71" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="N71" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="O71" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P71" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.09</v>
+        <v>4.5</v>
       </c>
       <c r="R71" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S71" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="T71" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U71" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V71" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W71" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="X71" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.85</v>
+        <v>3.27</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AA71" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9633,20 +9633,20 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['68', '71']</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45809.64583333334</v>
@@ -9673,109 +9673,109 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
         <v>2</v>
       </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="M72" t="n">
-        <v>2.83</v>
+        <v>3.39</v>
       </c>
       <c r="N72" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O72" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="P72" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="Q72" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="R72" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S72" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="T72" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U72" t="n">
         <v>1.25</v>
       </c>
       <c r="V72" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="W72" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD72" t="n">
         <v>1.57</v>
       </c>
-      <c r="X72" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['22', '36', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['22', '26']</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH72" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ72" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45809.64583333334</v>
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="n">
         <v>1</v>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y73" t="n">
         <v>3</v>
       </c>
-      <c r="M73" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="N73" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O73" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P73" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T73" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V73" t="n">
+      <c r="Z73" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AB73" t="n">
         <v>1.1</v>
       </c>
-      <c r="W73" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z73" t="n">
+      <c r="AC73" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>['20', '60']</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA73" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AG73" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH73" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AI73" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ73" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45809.64583333334</v>
@@ -10060,25 +10060,25 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
         <v>1</v>
       </c>
-      <c r="H75" t="n">
-        <v>2</v>
-      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -10086,83 +10086,83 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="N75" t="n">
-        <v>3.01</v>
+        <v>2.25</v>
       </c>
       <c r="O75" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="P75" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.5</v>
+        <v>2.87</v>
       </c>
       <c r="R75" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S75" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="T75" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U75" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V75" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="W75" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Y75" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AA75" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>['20', '60']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45809.64583333334</v>
@@ -10189,25 +10189,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
         <v>2</v>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -10215,83 +10215,83 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="M76" t="n">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="N76" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O76" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="P76" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W76" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S76" t="n">
+      <c r="X76" t="n">
         <v>2.15</v>
       </c>
-      <c r="T76" t="n">
-        <v>4</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X76" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y76" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA76" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '36', '63']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['68', '71']</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45809.64583333334</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,19 +10318,19 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -10344,83 +10344,83 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="N77" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="P77" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC77" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q77" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U77" t="n">
+      <c r="AD77" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>['26', '47', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
         <v>1.4</v>
-      </c>
-      <c r="V77" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W77" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X77" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG77" t="n">
-        <v>1.39</v>
       </c>
       <c r="AH77" t="n">
         <v>1.57</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ77" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45809.66666666666</v>
@@ -10447,25 +10447,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -10473,58 +10473,58 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="M78" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="O78" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P78" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R78" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S78" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T78" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U78" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V78" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W78" t="n">
         <v>1.4</v>
       </c>
       <c r="X78" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AA78" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD78" t="n">
         <v>1.83</v>
@@ -10536,20 +10536,20 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['13', '38']</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH78" t="n">
         <v>1.44</v>
       </c>
       <c r="AI78" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ78" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45809.66666666666</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,16 +10576,16 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -10594,7 +10594,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -10602,83 +10602,83 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="M79" t="n">
-        <v>3.26</v>
+        <v>2.84</v>
       </c>
       <c r="N79" t="n">
-        <v>2.77</v>
+        <v>1.89</v>
       </c>
       <c r="O79" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="P79" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R79" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S79" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="T79" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="U79" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="V79" t="n">
         <v>1.08</v>
       </c>
       <c r="W79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH79" t="n">
         <v>1.33</v>
       </c>
-      <c r="X79" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI79" t="n">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45809.66666666666</v>
@@ -10695,32 +10695,32 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -10731,83 +10731,83 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="M80" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="O80" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="P80" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.67</v>
+        <v>4.33</v>
       </c>
       <c r="R80" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="S80" t="n">
-        <v>2.31</v>
+        <v>3.45</v>
       </c>
       <c r="T80" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="U80" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="V80" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W80" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="X80" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA80" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y80" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>5</v>
-      </c>
       <c r="AB80" t="n">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>['17', '26']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>['9', '62']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>45809.66666666666</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,109 +10834,109 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.2</v>
+        <v>2.47</v>
       </c>
       <c r="M81" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="N81" t="n">
-        <v>1.89</v>
+        <v>2.98</v>
       </c>
       <c r="O81" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="P81" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.15</v>
+        <v>3.67</v>
       </c>
       <c r="R81" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S81" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="T81" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="U81" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V81" t="n">
         <v>1.08</v>
       </c>
       <c r="W81" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X81" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AA81" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AB81" t="n">
         <v>1.13</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD81" t="n">
         <v>1.62</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '26']</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['9', '62']</t>
         </is>
       </c>
       <c r="AG81" t="n">
         <v>1.4</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AI81" t="n">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45809.66666666666</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
@@ -10981,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -10989,80 +10989,80 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="O82" t="n">
         <v>3</v>
       </c>
       <c r="P82" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="R82" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S82" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T82" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U82" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V82" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W82" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="X82" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y82" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD82" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z82" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>['35', '57']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ82" t="n">
         <v>2.2</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,25 +11092,25 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -11118,83 +11118,83 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="M83" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>3.37</v>
+        <v>2.73</v>
       </c>
       <c r="O83" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="P83" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="R83" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S83" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="T83" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="U83" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V83" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="W83" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="X83" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA83" t="n">
-        <v>5.74</v>
+        <v>4.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC83" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>['35', '57']</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AG83" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ83" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>['26', '47', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG83" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK83" s="3" t="n">
         <v>45809.66666666666</v>
@@ -11211,26 +11211,26 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>1</v>
@@ -11239,7 +11239,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -11247,83 +11247,83 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="N84" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="O84" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P84" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="Q84" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S84" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T84" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X84" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA84" t="n">
         <v>4.33</v>
       </c>
-      <c r="R84" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S84" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T84" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U84" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V84" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X84" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AB84" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH84" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>45809.66666666666</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,25 +11350,25 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -11376,83 +11376,83 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="M85" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="N85" t="n">
-        <v>2.31</v>
+        <v>2.77</v>
       </c>
       <c r="O85" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P85" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R85" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S85" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T85" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U85" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V85" t="n">
         <v>1.08</v>
       </c>
       <c r="W85" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X85" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AA85" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC85" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD85" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD85" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>['13', '38']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI85" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AK85" s="3" t="n">
         <v>45809.66666666666</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12400,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -12408,55 +12408,55 @@
         </is>
       </c>
       <c r="L93" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T93" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X93" t="n">
         <v>2.75</v>
       </c>
-      <c r="M93" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N93" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O93" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S93" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T93" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="U93" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V93" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W93" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X93" t="n">
-        <v>2.33</v>
-      </c>
       <c r="Y93" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AA93" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AC93" t="n">
         <v>2.1</v>
@@ -12471,20 +12471,20 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AI93" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AK93" s="3" t="n">
         <v>45809.77083333334</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12529,7 +12529,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -12537,55 +12537,55 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.13</v>
+        <v>2.75</v>
       </c>
       <c r="M94" t="n">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
       <c r="N94" t="n">
-        <v>1.94</v>
+        <v>2.85</v>
       </c>
       <c r="O94" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="P94" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.63</v>
+        <v>3.55</v>
       </c>
       <c r="R94" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S94" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T94" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="U94" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V94" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W94" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="X94" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AA94" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AC94" t="n">
         <v>2.1</v>
@@ -12600,20 +12600,20 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AI94" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AJ94" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AK94" s="3" t="n">
         <v>45809.77083333334</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,19 +13027,19 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -13053,83 +13053,83 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="M98" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>4.2</v>
+        <v>5.17</v>
       </c>
       <c r="O98" t="n">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="P98" t="n">
         <v>2.15</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.45</v>
+        <v>5.7</v>
       </c>
       <c r="R98" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S98" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="T98" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U98" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V98" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W98" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X98" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y98" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA98" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>['55', '83']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>['51', '54', '58']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AK98" s="3" t="n">
         <v>45809.79166666666</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,19 +13156,19 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -13182,83 +13182,83 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="N99" t="n">
-        <v>5.17</v>
+        <v>3.32</v>
       </c>
       <c r="O99" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="P99" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S99" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="T99" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="U99" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V99" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W99" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X99" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Y99" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD99" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z99" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC99" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['55', '83']</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['51', '54', '58']</t>
         </is>
       </c>
       <c r="AG99" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH99" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AK99" s="3" t="n">
         <v>45809.79166666666</v>
